--- a/data/transformations--response_times.xlsx
+++ b/data/transformations--response_times.xlsx
@@ -8062,7 +8062,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Symmetric, transformed features are what many models and tests assume.</t>
+          <t>Many models and tests work best when their errors are roughly symmetric, which a transform often helps with.</t>
         </is>
       </c>
     </row>
